--- a/InputFiles/ICDC/ICDC_StaticData.xlsx
+++ b/InputFiles/ICDC/ICDC_StaticData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leungvw/git/Commons_Automation/InputFiles/ICDC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44254749-EC33-5A47-8498-A77C24D2EF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD803AC-0F9B-9B45-9C66-27E0F5C122B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="2060" windowWidth="33260" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="V_HomePage" sheetId="1" r:id="rId1"/>
@@ -129,12 +129,6 @@
     <t>verificationUrl</t>
   </si>
   <si>
-    <t>Integrated Canine Data Commons</t>
-  </si>
-  <si>
-    <t>Exploring, analyzing, and understanding the biological relationships between human and canine cancers.</t>
-  </si>
-  <si>
     <t>https://caninecommons-qa.cancer.gov/#/submit</t>
   </si>
   <si>
@@ -480,16 +474,7 @@
     <t>https://www.cancer.gov/</t>
   </si>
   <si>
-    <t>Submit Data Interested in contributing data to ICDC?</t>
-  </si>
-  <si>
-    <t>Programs Discover the programs in ICDC</t>
-  </si>
-  <si>
     <t>About ICDC Comparative oncology research and more</t>
-  </si>
-  <si>
-    <t>ICDC News Updates and announcements</t>
   </si>
   <si>
     <t>SpotlightPanelLink1</t>
@@ -878,6 +863,21 @@
   </si>
   <si>
     <t>SupportDescription</t>
+  </si>
+  <si>
+    <t>Why Canine Cancer data? ICDC studies highlight  the impact of canine research on human cancer research</t>
+  </si>
+  <si>
+    <t>Canine cancer research plays a pivotal role in advancing human cancer research. Explore how pet dogs with spontaneous tumors offer unique opportunities for the cancer research community to gain significant insights into understanding cancer biology, developing new treatments, mitigating toxicities, and improving outcomes for both canines and humans.</t>
+  </si>
+  <si>
+    <t>Submit Data Interested in contributing data to the ICDC?</t>
+  </si>
+  <si>
+    <t>Programs Discover programs within the ICDC</t>
+  </si>
+  <si>
+    <t>ICDC Spotlight Updates and announcements</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -1250,51 +1250,51 @@
         <v>8</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>278</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1305,7 +1305,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1319,13 +1319,13 @@
     </row>
     <row r="10" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1339,35 +1339,35 @@
     </row>
     <row r="12" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1387,7 +1387,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1398,7 +1398,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14" x14ac:dyDescent="0.15">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="23" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4"/>
     </row>
@@ -1510,48 +1510,48 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="84" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1585,176 +1585,176 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" ht="98" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="84" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="140" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -1795,16 +1795,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C3" s="8"/>
     </row>
@@ -1844,73 +1844,73 @@
     </row>
     <row r="3" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1944,197 +1944,197 @@
         <v>6</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="C19" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2177,150 +2177,150 @@
         <v>6</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" ht="112" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C4" s="8"/>
     </row>
     <row r="5" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="84" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="84" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="98" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="84" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="182" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="C16" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2360,106 +2360,106 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="56" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2502,46 +2502,46 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="154" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="98" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2579,46 +2579,46 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="70" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2656,46 +2656,46 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="140" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2733,35 +2733,35 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="98" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
